--- a/Dependencies/Ping_2018/PTM_heatmap_data.xlsx
+++ b/Dependencies/Ping_2018/PTM_heatmap_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,20 +456,25 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>fcb1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>fcb2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>fcb3</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>fcb4</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>fcb5</t>
         </is>
@@ -482,881 +487,1477 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.940467897675515</v>
+        <v>3.094210121833379</v>
       </c>
       <c r="C2" t="n">
-        <v>5.095687373343774</v>
+        <v>3.078434802042492</v>
       </c>
       <c r="D2" t="n">
-        <v>5.080130593223783</v>
+        <v>3.065162364716226</v>
       </c>
       <c r="E2" t="n">
-        <v>6.543230717506919</v>
+        <v>3.657582719527119</v>
       </c>
       <c r="F2" t="n">
-        <v>5.139199798215468</v>
+        <v>3.35058309664208</v>
       </c>
       <c r="G2" t="n">
-        <v>5.758500444035679</v>
+        <v>4.247442652401829</v>
       </c>
       <c r="H2" t="n">
-        <v>4.883661922511191</v>
+        <v>4.709014664925133</v>
       </c>
       <c r="I2" t="n">
-        <v>3.291802244998721</v>
+        <v>4.959523478730503</v>
       </c>
       <c r="J2" t="n">
-        <v>5.00884674260949</v>
+        <v>3.718868507295042</v>
+      </c>
+      <c r="K2" t="n">
+        <v>5.237062575097453</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Deamidation</t>
+          <t>Dihydroxy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7126705318772706</v>
+        <v>0.3332883658554004</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9616535122511111</v>
+        <v>0.3315891501115014</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2744743021962067</v>
+        <v>0.3301595287305306</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2645664019111199</v>
+        <v>0.3939712299983837</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2318682935544556</v>
+        <v>0.3609032098572846</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4877876224821688</v>
+        <v>0.4575071391223907</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1329524526450516</v>
+        <v>0.5072247005423403</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3070960757136824</v>
+        <v>0.5342078949273732</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1809109162839705</v>
+        <v>0.4005725399453725</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.5641026170848706</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Dihydroxy</t>
+          <t>Sodium adduct</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5924036584944731</v>
+        <v>0.2685840310922641</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9432940969415112</v>
+        <v>0.2672146997235543</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7144577866180232</v>
+        <v>0.2660626238854092</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4156458753885154</v>
+        <v>0.3174859728924704</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3133177791089952</v>
+        <v>0.2908377515333429</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3704951789082122</v>
+        <v>0.3686870718202416</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4044750672018472</v>
+        <v>0.4087525059315563</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5323990077748101</v>
+        <v>0.4304972047033776</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5248404604282221</v>
+        <v>0.3228057098460877</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.4545881895922034</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>DTT adduct of cysteine</t>
+          <t>Deamidation</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1452728569574386</v>
+        <v>0.1117065402042826</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1601700714940955</v>
+        <v>0.1111370228395692</v>
       </c>
       <c r="D5" t="n">
-        <v>0.148428163419408</v>
+        <v>0.1106578640250679</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1078125820120381</v>
+        <v>0.1320453023620956</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08801799245409929</v>
+        <v>0.1209620648422767</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004654462046585579</v>
+        <v>0.1533403048706914</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002808854633346161</v>
+        <v>0.1700038831488064</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001487148066410084</v>
+        <v>0.1790477010470866</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02485040058845748</v>
+        <v>0.1342578293223501</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.1890673606713028</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Sodium adduct</t>
+          <t>Iodoacetamide derivative</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1250299178732054</v>
+        <v>0.08118562758016165</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1456091559037232</v>
+        <v>0.08077171605280163</v>
       </c>
       <c r="D6" t="n">
-        <v>0.09424010375835425</v>
+        <v>0.08042347494718052</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03688325174096041</v>
+        <v>0.09596735089704218</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02627402759823859</v>
+        <v>0.08791232034985137</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3174343115771365</v>
+        <v>0.1114440467093003</v>
       </c>
       <c r="H6" t="n">
-        <v>0.08801077851151304</v>
+        <v>0.1235547347474931</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03792227569345714</v>
+        <v>0.1301275641489755</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3260372557205622</v>
+        <v>0.0975753622943856</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.1374096118540069</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Oxidation to nitro</t>
+          <t>Replacement of proton with ammonium ion</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1125269260858848</v>
+        <v>0.06226266175320668</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1367459898921922</v>
+        <v>0.06194522584500576</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1896582088136879</v>
+        <v>0.06167815371889033</v>
       </c>
       <c r="E7" t="n">
-        <v>0.09575459586595492</v>
+        <v>0.07359902098870905</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06305766623577262</v>
+        <v>0.06742147876454767</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1238086904391764</v>
+        <v>0.08546836664923783</v>
       </c>
       <c r="H7" t="n">
-        <v>0.07396650534478223</v>
+        <v>0.09475626273867896</v>
       </c>
       <c r="I7" t="n">
-        <v>0.05056303425794285</v>
+        <v>0.09979707927214664</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1013896344009065</v>
+        <v>0.07483223273704762</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.1053818075872835</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Dehydration</t>
+          <t>Oxidation to nitro</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1000239342985643</v>
+        <v>0.06165224350072426</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1399114063248819</v>
+        <v>0.0613379197092704</v>
       </c>
       <c r="D8" t="n">
-        <v>0.06184506809141997</v>
+        <v>0.06107346593733257</v>
       </c>
       <c r="E8" t="n">
-        <v>0.06099922403312683</v>
+        <v>0.07287746195940797</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03875419070740192</v>
+        <v>0.06676048387469917</v>
       </c>
       <c r="G8" t="n">
-        <v>0.09867459538761428</v>
+        <v>0.08463044148601001</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03651511023350008</v>
+        <v>0.09382727977065268</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04238371989268739</v>
+        <v>0.09881867653418441</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03479056082384048</v>
+        <v>0.07409858339648831</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.1043486526109376</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2-amino-3-oxo-butanoic_acid</t>
+          <t>Methylation</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.07859023409172909</v>
+        <v>0.03601467689646268</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1088903252845235</v>
+        <v>0.03583106200838568</v>
       </c>
       <c r="D9" t="n">
-        <v>0.08069308884309082</v>
+        <v>0.03567657911190714</v>
       </c>
       <c r="E9" t="n">
-        <v>0.05674346421686217</v>
+        <v>0.04257198272876307</v>
       </c>
       <c r="F9" t="n">
-        <v>0.06634191968555245</v>
+        <v>0.03899869850106188</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02513409505156213</v>
+        <v>0.04943758463044148</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01872569755564107</v>
+        <v>0.05480999511354959</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0282558132617916</v>
+        <v>0.05772576153977109</v>
       </c>
       <c r="J9" t="n">
-        <v>0.02385638456491919</v>
+        <v>0.04328531109299812</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.06095614360440909</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Acrylamide adduct</t>
+          <t>Addition of Glycine</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.07263642847871932</v>
+        <v>0.03174174912908576</v>
       </c>
       <c r="C10" t="n">
-        <v>0.08040157739031673</v>
+        <v>0.03157991905823822</v>
       </c>
       <c r="D10" t="n">
-        <v>0.07892608689762168</v>
+        <v>0.03144376464100291</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0773129699954747</v>
+        <v>0.03752106952365559</v>
       </c>
       <c r="F10" t="n">
-        <v>0.04729324967682947</v>
+        <v>0.03437173427212234</v>
       </c>
       <c r="G10" t="n">
-        <v>0.02420320264224501</v>
+        <v>0.04357210848784673</v>
       </c>
       <c r="H10" t="n">
-        <v>0.005617709266692321</v>
+        <v>0.04830711433736574</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01189718453128067</v>
+        <v>0.05087694237403553</v>
       </c>
       <c r="J10" t="n">
-        <v>0.004970080117691497</v>
+        <v>0.03814976570908309</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.05372405876998767</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Replacement of proton with ammonium ion</t>
+          <t>Carbamylation</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.06608724230440856</v>
+        <v>0.02930007611915608</v>
       </c>
       <c r="C11" t="n">
-        <v>0.07280457795186161</v>
+        <v>0.02915069451529683</v>
       </c>
       <c r="D11" t="n">
-        <v>0.03534003890938284</v>
+        <v>0.02902501351477191</v>
       </c>
       <c r="E11" t="n">
-        <v>0.007092933027107771</v>
+        <v>0.03463483340645131</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01182331241920737</v>
+        <v>0.03172775471272832</v>
       </c>
       <c r="G11" t="n">
-        <v>0.08098763961058908</v>
+        <v>0.04022040783493545</v>
       </c>
       <c r="H11" t="n">
-        <v>0.09924619704489768</v>
+        <v>0.04459118246526068</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1018696425490908</v>
+        <v>0.04696333142218665</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1182879068010576</v>
+        <v>0.03521516834684593</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.04959143886460401</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Methylation</t>
+          <t>Dehydration</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05001196714928215</v>
+        <v>0.02380631184681432</v>
       </c>
       <c r="C12" t="n">
-        <v>0.05507824592879965</v>
+        <v>0.02368493929367867</v>
       </c>
       <c r="D12" t="n">
-        <v>0.04417504863672855</v>
+        <v>0.02358282348075218</v>
       </c>
       <c r="E12" t="n">
-        <v>0.03617395843824964</v>
+        <v>0.02814080214274169</v>
       </c>
       <c r="F12" t="n">
-        <v>0.02693087828819456</v>
+        <v>0.02577880070409175</v>
       </c>
       <c r="G12" t="n">
-        <v>0.02141052541429367</v>
+        <v>0.03267908136588505</v>
       </c>
       <c r="H12" t="n">
-        <v>0.03183368584458982</v>
+        <v>0.03623033575302431</v>
       </c>
       <c r="I12" t="n">
-        <v>0.02974296132820168</v>
+        <v>0.03815770678052665</v>
       </c>
       <c r="J12" t="n">
-        <v>0.05168883322399156</v>
+        <v>0.02861232428181232</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.04029304407749076</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Missing TMT10_Nterm_mono</t>
+          <t>Replacement of 2 protons by calcium</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03750897536196161</v>
+        <v>0.02075422058440222</v>
       </c>
       <c r="C13" t="n">
-        <v>0.02595641474805501</v>
+        <v>0.02064840861500192</v>
       </c>
       <c r="D13" t="n">
-        <v>0.01767001945469142</v>
+        <v>0.02055938457296344</v>
       </c>
       <c r="E13" t="n">
-        <v>0.01631374596234787</v>
+        <v>0.02453300699623635</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0223329234585028</v>
+        <v>0.02247382625484922</v>
       </c>
       <c r="G13" t="n">
-        <v>0.01582517095839097</v>
+        <v>0.02848945554974594</v>
       </c>
       <c r="H13" t="n">
-        <v>0.005617709266692321</v>
+        <v>0.03158542091289298</v>
       </c>
       <c r="I13" t="n">
-        <v>0.005948592265640336</v>
+        <v>0.03326569309071554</v>
       </c>
       <c r="J13" t="n">
-        <v>0.01391622432953619</v>
+        <v>0.02494407757901587</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.03512726919576117</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Phosphorylation</t>
+          <t>Reduction</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.03274593087155379</v>
+        <v>0.02075422058440222</v>
       </c>
       <c r="C14" t="n">
-        <v>0.002532333146151708</v>
+        <v>0.02064840861500192</v>
       </c>
       <c r="D14" t="n">
-        <v>0.006479007133386855</v>
+        <v>0.02055938457296344</v>
       </c>
       <c r="E14" t="n">
-        <v>0.003546466513553885</v>
+        <v>0.02453300699623635</v>
       </c>
       <c r="F14" t="n">
-        <v>0.003284253449779824</v>
+        <v>0.02247382625484922</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0009308924093171159</v>
+        <v>0.02848945554974594</v>
       </c>
       <c r="H14" t="n">
-        <v>0.005617709266692321</v>
+        <v>0.03158542091289298</v>
       </c>
       <c r="I14" t="n">
-        <v>0.005948592265640336</v>
+        <v>0.03326569309071554</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0009940160235382993</v>
+        <v>0.02494407757901587</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.03512726919576117</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Conversion of carboxylic acid to hydroxamic acid</t>
+          <t>Cysteine oxidation to cysteic acid</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.02619674469724303</v>
+        <v>0.01587087456454288</v>
       </c>
       <c r="C15" t="n">
-        <v>0.02215791502882745</v>
+        <v>0.01578995952911911</v>
       </c>
       <c r="D15" t="n">
-        <v>0.03003903307297542</v>
+        <v>0.01572188232050145</v>
       </c>
       <c r="E15" t="n">
-        <v>0.01134869284337243</v>
+        <v>0.01876053476182779</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02758772897815052</v>
+        <v>0.01718586713606117</v>
       </c>
       <c r="G15" t="n">
-        <v>0.001861784818634232</v>
+        <v>0.02178605424392337</v>
       </c>
       <c r="H15" t="n">
-        <v>0.007490279022256428</v>
+        <v>0.02415355716868287</v>
       </c>
       <c r="I15" t="n">
-        <v>0.01933292486333109</v>
+        <v>0.02543847118701777</v>
       </c>
       <c r="J15" t="n">
-        <v>0.002982048070614898</v>
+        <v>0.01907488285454155</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.02686202938499383</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Quinone</t>
+          <t>2-amino-3-oxo-butanoic_acid</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02560136413594205</v>
+        <v>0.01403961980709562</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0303879977538205</v>
+        <v>0.01396804112191306</v>
       </c>
       <c r="D16" t="n">
-        <v>0.02414902658807827</v>
+        <v>0.01390781897582821</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0184416258704802</v>
+        <v>0.01659585767392459</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0131370137991193</v>
+        <v>0.01520288246651565</v>
       </c>
       <c r="G16" t="n">
-        <v>0.01954874059565943</v>
+        <v>0.0192722787542399</v>
       </c>
       <c r="H16" t="n">
-        <v>0.01966198243342312</v>
+        <v>0.02136660826460408</v>
       </c>
       <c r="I16" t="n">
-        <v>0.03197368342781681</v>
+        <v>0.0225032629731311</v>
       </c>
       <c r="J16" t="n">
-        <v>0.01192819228245959</v>
+        <v>0.01687393483286368</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.02376256445595609</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Carbamylation</t>
+          <t>Replacement of 2 protons by magnesium</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.02560136413594205</v>
+        <v>0.01159794679716595</v>
       </c>
       <c r="C17" t="n">
-        <v>0.03355341418651013</v>
+        <v>0.01153881657897166</v>
       </c>
       <c r="D17" t="n">
-        <v>0.02473802723656799</v>
+        <v>0.01148906784959722</v>
       </c>
       <c r="E17" t="n">
-        <v>0.02198809238403409</v>
+        <v>0.01370962155672031</v>
       </c>
       <c r="F17" t="n">
-        <v>0.02364662483841473</v>
+        <v>0.01255890290712162</v>
       </c>
       <c r="G17" t="n">
-        <v>0.02420320264224501</v>
+        <v>0.01592057810132861</v>
       </c>
       <c r="H17" t="n">
-        <v>0.02247083706676928</v>
+        <v>0.01765067639249902</v>
       </c>
       <c r="I17" t="n">
-        <v>0.06617808895524874</v>
+        <v>0.01858965202128221</v>
       </c>
       <c r="J17" t="n">
-        <v>0.02584441661199578</v>
+        <v>0.01393933747062651</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.01962994455057242</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Reduction</t>
+          <t>DTT adduct of cysteine</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.02321984189073814</v>
+        <v>0.01159794679716595</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01835941530959988</v>
+        <v>0.01153881657897166</v>
       </c>
       <c r="D18" t="n">
-        <v>0.04240804669125942</v>
+        <v>0.01148906784959722</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0312089053192742</v>
+        <v>0.01370962155672031</v>
       </c>
       <c r="F18" t="n">
-        <v>0.02167607276854684</v>
+        <v>0.01255890290712162</v>
       </c>
       <c r="G18" t="n">
-        <v>0.02141052541429367</v>
+        <v>0.01592057810132861</v>
       </c>
       <c r="H18" t="n">
-        <v>0.008426563900038483</v>
+        <v>0.01765067639249902</v>
       </c>
       <c r="I18" t="n">
-        <v>0.02379436906256134</v>
+        <v>0.01858965202128221</v>
       </c>
       <c r="J18" t="n">
-        <v>0.02485040058845748</v>
+        <v>0.01393933747062651</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.01962994455057242</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Replacement of 2 protons by magnesium</t>
+          <t>Loss of ammonia</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.01964755852293227</v>
+        <v>0.01159794679716595</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02215791502882745</v>
+        <v>0.01153881657897166</v>
       </c>
       <c r="D19" t="n">
-        <v>0.01767001945469142</v>
+        <v>0.01148906784959722</v>
       </c>
       <c r="E19" t="n">
-        <v>0.01489515935692632</v>
+        <v>0.01370962155672031</v>
       </c>
       <c r="F19" t="n">
-        <v>0.007882208279471578</v>
+        <v>0.01255890290712162</v>
       </c>
       <c r="G19" t="n">
-        <v>0.01954874059565943</v>
+        <v>0.01592057810132861</v>
       </c>
       <c r="H19" t="n">
-        <v>0.001872569755564107</v>
+        <v>0.01765067639249902</v>
       </c>
       <c r="I19" t="n">
-        <v>0.004461444199230252</v>
+        <v>0.01858965202128221</v>
       </c>
       <c r="J19" t="n">
-        <v>0.01292220830599789</v>
+        <v>0.01393933747062651</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.01962994455057242</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Loss of ammonia</t>
+          <t>Half of a disulfide bridge</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.01845679740033032</v>
+        <v>0.01159794679716595</v>
       </c>
       <c r="C20" t="n">
-        <v>0.01772633202306196</v>
+        <v>0.01153881657897166</v>
       </c>
       <c r="D20" t="n">
-        <v>0.01413601556375314</v>
+        <v>0.01148906784959722</v>
       </c>
       <c r="E20" t="n">
-        <v>0.005674346421686217</v>
+        <v>0.01370962155672031</v>
       </c>
       <c r="F20" t="n">
-        <v>0.01248016310916333</v>
+        <v>0.01255890290712162</v>
       </c>
       <c r="G20" t="n">
-        <v>0.007447139274536927</v>
+        <v>0.01592057810132861</v>
       </c>
       <c r="H20" t="n">
-        <v>0.01498055804451286</v>
+        <v>0.01765067639249902</v>
       </c>
       <c r="I20" t="n">
-        <v>0.01264075856448571</v>
+        <v>0.01858965202128221</v>
       </c>
       <c r="J20" t="n">
-        <v>0.01491024035307449</v>
+        <v>0.01393933747062651</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.01962994455057242</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Cysteine oxidation to cysteic acid</t>
+          <t>Replacement of 3 protons by iron</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.01250299178732054</v>
+        <v>0.01037711029220111</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0164601654499861</v>
+        <v>0.01032420430750096</v>
       </c>
       <c r="D21" t="n">
-        <v>0.03003903307297542</v>
+        <v>0.01027969228648172</v>
       </c>
       <c r="E21" t="n">
-        <v>0.009220812935240102</v>
+        <v>0.01226650349811817</v>
       </c>
       <c r="F21" t="n">
-        <v>0.01707811793885508</v>
+        <v>0.01123691312742461</v>
       </c>
       <c r="G21" t="n">
-        <v>0.01117070891180539</v>
+        <v>0.01424472777487297</v>
       </c>
       <c r="H21" t="n">
-        <v>0.01872569755564107</v>
+        <v>0.01579271045644649</v>
       </c>
       <c r="I21" t="n">
-        <v>0.008922888398460505</v>
+        <v>0.01663284654535777</v>
       </c>
       <c r="J21" t="n">
-        <v>0.02584441661199578</v>
+        <v>0.01247203878950793</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.01756363459788059</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Prompt loss of side chain from oxidised Met</t>
+          <t>Replacement of proton by potassium</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.01131223066471858</v>
+        <v>0.005493764272341765</v>
       </c>
       <c r="C22" t="n">
-        <v>0.009496249298068905</v>
+        <v>0.005465755221618155</v>
       </c>
       <c r="D22" t="n">
-        <v>0.01531401686073256</v>
+        <v>0.005442190034019734</v>
       </c>
       <c r="E22" t="n">
-        <v>0.02411597229216642</v>
+        <v>0.006494031263709622</v>
       </c>
       <c r="F22" t="n">
-        <v>0.02496032621832666</v>
+        <v>0.00594895400863656</v>
       </c>
       <c r="G22" t="n">
-        <v>0.001861784818634232</v>
+        <v>0.007541326469050397</v>
       </c>
       <c r="H22" t="n">
-        <v>0.004681424388910268</v>
+        <v>0.008360846712236379</v>
       </c>
       <c r="I22" t="n">
-        <v>0.002230722099615126</v>
+        <v>0.008805624641659997</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0009940160235382993</v>
+        <v>0.006602844065033612</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.009298394787113253</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Half of a disulfide bridge</t>
+          <t>Quinone</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.01131223066471858</v>
+        <v>0.005493764272341765</v>
       </c>
       <c r="C23" t="n">
-        <v>0.009496249298068905</v>
+        <v>0.005465755221618155</v>
       </c>
       <c r="D23" t="n">
-        <v>0.01001301102432514</v>
+        <v>0.005442190034019734</v>
       </c>
       <c r="E23" t="n">
-        <v>0.01773233256776943</v>
+        <v>0.006494031263709622</v>
       </c>
       <c r="F23" t="n">
-        <v>0.001970552069867894</v>
+        <v>0.00594895400863656</v>
       </c>
       <c r="G23" t="n">
-        <v>0.005585354455902695</v>
+        <v>0.007541326469050397</v>
       </c>
       <c r="H23" t="n">
-        <v>0.003745139511128214</v>
+        <v>0.008360846712236379</v>
       </c>
       <c r="I23" t="n">
-        <v>0.009666462431665546</v>
+        <v>0.008805624641659997</v>
       </c>
       <c r="J23" t="n">
-        <v>0.01789228842368939</v>
+        <v>0.006602844065033612</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.009298394787113253</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Deamidation followed by a methylation</t>
+          <t>Amidation</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.0107168501034176</v>
+        <v>0.004272927767376929</v>
       </c>
       <c r="C24" t="n">
-        <v>0.01582708216344817</v>
+        <v>0.004251142950147454</v>
       </c>
       <c r="D24" t="n">
-        <v>0.01178001296979428</v>
+        <v>0.004232814470904238</v>
       </c>
       <c r="E24" t="n">
-        <v>0.006383639724396995</v>
+        <v>0.005050913205107484</v>
       </c>
       <c r="F24" t="n">
-        <v>0.002627402759823859</v>
+        <v>0.004626964228939546</v>
       </c>
       <c r="G24" t="n">
-        <v>0.009308924093171158</v>
+        <v>0.005865476142594753</v>
       </c>
       <c r="H24" t="n">
-        <v>0.004681424388910268</v>
+        <v>0.00650288077618385</v>
       </c>
       <c r="I24" t="n">
-        <v>0.01041003646487059</v>
+        <v>0.006848819165735554</v>
       </c>
       <c r="J24" t="n">
-        <v>0.005964096141229796</v>
+        <v>0.005135545383915032</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.007232084834421419</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Persulfide</t>
+          <t>Missing TMT10_Nterm_mono</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.007144566735611736</v>
+        <v>0.00366250951489451</v>
       </c>
       <c r="C25" t="n">
-        <v>0.005697749578841343</v>
+        <v>0.003643836814412103</v>
       </c>
       <c r="D25" t="n">
-        <v>0.008835009727345711</v>
+        <v>0.003628126689346489</v>
       </c>
       <c r="E25" t="n">
-        <v>0.008511519632529324</v>
+        <v>0.004329354175806414</v>
       </c>
       <c r="F25" t="n">
-        <v>0.009852760349339473</v>
+        <v>0.00396596933909104</v>
       </c>
       <c r="G25" t="n">
-        <v>0.002792677227951347</v>
+        <v>0.005027550979366931</v>
       </c>
       <c r="H25" t="n">
-        <v>0.001872569755564107</v>
+        <v>0.005573897808157586</v>
       </c>
       <c r="I25" t="n">
-        <v>0.00371787016602521</v>
+        <v>0.005870416427773331</v>
       </c>
       <c r="J25" t="n">
-        <v>0.004970080117691497</v>
+        <v>0.004401896043355742</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.006198929858075501</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Missing TMT10_Lys_mono</t>
+          <t>Acrylamide adduct</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.00595380561300978</v>
+        <v>0.00366250951489451</v>
       </c>
       <c r="C26" t="n">
-        <v>0.01012933258460683</v>
+        <v>0.003643836814412103</v>
       </c>
       <c r="D26" t="n">
-        <v>0.01178001296979428</v>
+        <v>0.003628126689346489</v>
       </c>
       <c r="E26" t="n">
-        <v>0.007802226329818549</v>
+        <v>0.004329354175806414</v>
       </c>
       <c r="F26" t="n">
-        <v>0.01050961103929544</v>
+        <v>0.00396596933909104</v>
       </c>
       <c r="G26" t="n">
-        <v>0.004654462046585579</v>
+        <v>0.005027550979366931</v>
       </c>
       <c r="H26" t="n">
-        <v>0.001872569755564107</v>
+        <v>0.005573897808157586</v>
       </c>
       <c r="I26" t="n">
-        <v>0.004461444199230252</v>
+        <v>0.005870416427773331</v>
       </c>
       <c r="J26" t="n">
-        <v>0.005964096141229796</v>
+        <v>0.004401896043355742</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.006198929858075501</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Iodoacetamide derivative</t>
+          <t>Acetaldehyde +26</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.001786141683902934</v>
+        <v>0.003052091262412092</v>
       </c>
       <c r="C27" t="n">
-        <v>0.005697749578841343</v>
+        <v>0.003036530678676753</v>
       </c>
       <c r="D27" t="n">
-        <v>0.00589000648489714</v>
+        <v>0.003023438907788741</v>
       </c>
       <c r="E27" t="n">
-        <v>0.006383639724396995</v>
+        <v>0.003607795146505345</v>
       </c>
       <c r="F27" t="n">
-        <v>0.005254805519647718</v>
+        <v>0.003304974449242533</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1051908422528341</v>
+        <v>0.004189625816139109</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1029913365560259</v>
+        <v>0.004644914840131321</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2074571552642067</v>
+        <v>0.004892013689811109</v>
       </c>
       <c r="J27" t="n">
-        <v>0.106359714518598</v>
+        <v>0.003668246702796451</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.005165774881729584</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Deamidation followed by a methylation</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.003052091262412092</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.003036530678676753</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.003023438907788741</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.003607795146505345</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.003304974449242533</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.004189625816139109</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.004644914840131321</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.004892013689811109</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.003668246702796451</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.005165774881729584</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Persulfide</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.003052091262412092</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.003036530678676753</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.003023438907788741</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.003607795146505345</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.003304974449242533</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.004189625816139109</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.004644914840131321</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.004892013689811109</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.003668246702796451</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.005165774881729584</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Missing TMT10_Lys_mono</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0.003052091262412092</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.003036530678676753</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.003023438907788741</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.003607795146505345</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.003304974449242533</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.004189625816139109</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.004644914840131321</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.004892013689811109</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.003668246702796451</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.005165774881729584</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Beta-methylthiolation</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.002441673009929674</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.002429224542941402</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.002418751126230993</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.002886236117204276</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.002643979559394026</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.003351700652911287</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.003715931872105057</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.003913610951848888</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.002934597362237161</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.004132619905383667</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Conversion of carboxylic acid to hydroxamic acid</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.001831254757447255</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.001821918407206052</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.001814063344673245</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.002164677087903207</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.00198298466954552</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.002513775489683465</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.002786948904078793</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.002935208213886666</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.002200948021677871</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.003099464929037751</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Prompt loss of side chain from oxidised Met</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0.001220836504964837</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.001214612271470701</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.001209375563115496</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.001443118058602138</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.001321989779697013</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.001675850326455644</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.001857965936052528</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.001956805475924444</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.001467298681118581</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.002066309952691834</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Hydroxymethyl</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0.001220836504964837</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.001214612271470701</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.001209375563115496</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.001443118058602138</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.001321989779697013</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.001675850326455644</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.001857965936052528</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.001956805475924444</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.001467298681118581</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.002066309952691834</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Succinic anhydride labeling reagent light form (N-term &amp; K)</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.001220836504964837</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.001214612271470701</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.001209375563115496</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.001443118058602138</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.001321989779697013</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.001675850326455644</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.001857965936052528</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.001956805475924444</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.001467298681118581</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.002066309952691834</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>Ethylation</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.001220836504964837</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.001214612271470701</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.001209375563115496</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.001443118058602138</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.001321989779697013</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.001675850326455644</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.001857965936052528</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.001956805475924444</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.001467298681118581</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.002066309952691834</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Fluorination</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0.0006104182524824184</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.0006073061357353505</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.0006046877815577482</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.000721559029301069</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.0006609948898485065</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.0008379251632278218</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.0009289829680262641</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.0009784027379622219</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.0007336493405592903</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.001033154976345917</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Iodoacetic acid derivative</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.0006104182524824184</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.0006073061357353505</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.0006046877815577482</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.000721559029301069</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.0006609948898485065</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.0008379251632278218</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.0009289829680262641</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.0009784027379622219</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.0007336493405592903</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.001033154976345917</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Carboxyethyl</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0.0006104182524824184</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.0006073061357353505</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.0006046877815577482</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.000721559029301069</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.0006609948898485065</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.0008379251632278218</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.0009289829680262641</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.0009784027379622219</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.0007336493405592903</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.001033154976345917</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Acetylation</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0.0006104182524824184</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.0006073061357353505</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.0006046877815577482</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.000721559029301069</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.0006609948898485065</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.0008379251632278218</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.0009289829680262641</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.0009784027379622219</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.0007336493405592903</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.001033154976345917</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Glyoxal-derived AGE</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0.0006104182524824184</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.0006073061357353505</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.0006046877815577482</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.000721559029301069</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.0006609948898485065</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.0008379251632278218</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.0009289829680262641</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.0009784027379622219</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.0007336493405592903</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.001033154976345917</v>
       </c>
     </row>
   </sheetData>
